--- a/research/traditional_assets/database/data/bangladesh/bangladesh_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0147</v>
+        <v>0.01055</v>
       </c>
       <c r="E2">
-        <v>0.05305</v>
+        <v>-0.15405</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>64.59</v>
+        <v>39.77</v>
       </c>
       <c r="L2">
-        <v>0.2649693966295269</v>
+        <v>0.2007571933366986</v>
       </c>
       <c r="M2">
-        <v>28.25</v>
+        <v>12.842</v>
       </c>
       <c r="N2">
-        <v>0.07085527965889139</v>
+        <v>0.05333056478405315</v>
       </c>
       <c r="O2">
-        <v>0.4373742065335191</v>
+        <v>0.3229067136032185</v>
       </c>
       <c r="P2">
-        <v>28.25</v>
+        <v>12.842</v>
       </c>
       <c r="Q2">
-        <v>0.07085527965889139</v>
+        <v>0.05333056478405315</v>
       </c>
       <c r="R2">
-        <v>0.4373742065335191</v>
+        <v>0.3229067136032185</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>309.54</v>
+        <v>235.6</v>
       </c>
       <c r="V2">
-        <v>0.7763732129420617</v>
+        <v>0.978405315614618</v>
       </c>
       <c r="W2">
-        <v>0.1102123356926188</v>
+        <v>0.07105157104305654</v>
       </c>
       <c r="X2">
-        <v>0.1533664349255993</v>
+        <v>0.1779807571051479</v>
       </c>
       <c r="Y2">
-        <v>-0.04315409923298048</v>
+        <v>-0.1069291860620913</v>
       </c>
       <c r="Z2">
-        <v>0.2670508326029798</v>
+        <v>0.1750463903861447</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06910969159285622</v>
+        <v>0.08919000454041467</v>
       </c>
       <c r="AC2">
-        <v>-0.06910969159285622</v>
+        <v>-0.08919000454041467</v>
       </c>
       <c r="AD2">
-        <v>986.9000000000001</v>
+        <v>765.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>986.9000000000001</v>
+        <v>765.9</v>
       </c>
       <c r="AG2">
-        <v>677.3600000000001</v>
+        <v>530.3</v>
       </c>
       <c r="AH2">
-        <v>0.7122546189376443</v>
+        <v>0.7608026224297209</v>
       </c>
       <c r="AI2">
-        <v>0.7307122760254702</v>
+        <v>0.6292310220177456</v>
       </c>
       <c r="AJ2">
-        <v>0.6294816274185454</v>
+        <v>0.6877188432109973</v>
       </c>
       <c r="AK2">
-        <v>0.6506445353774039</v>
+        <v>0.5402404237978811</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ONE Bank Limited (DSE:ONEBANKLTD)</t>
+          <t>Mercantile Bank Limited (DSE:MERCANBANK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0147</v>
+        <v>0.0722</v>
       </c>
       <c r="E3">
-        <v>-0.0199</v>
+        <v>0.0249</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>21.8</v>
+        <v>35.8</v>
       </c>
       <c r="L3">
-        <v>0.2526071842410197</v>
+        <v>0.2681647940074906</v>
       </c>
       <c r="M3">
-        <v>9.35</v>
+        <v>12.8</v>
       </c>
       <c r="N3">
-        <v>0.06187954996690933</v>
+        <v>0.089198606271777</v>
       </c>
       <c r="O3">
-        <v>0.4288990825688073</v>
+        <v>0.3575418994413408</v>
       </c>
       <c r="P3">
-        <v>9.35</v>
+        <v>12.8</v>
       </c>
       <c r="Q3">
-        <v>0.06187954996690933</v>
+        <v>0.089198606271777</v>
       </c>
       <c r="R3">
-        <v>0.4288990825688073</v>
+        <v>0.3575418994413408</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>200.4</v>
+        <v>98.3</v>
       </c>
       <c r="V3">
-        <v>1.326273990734613</v>
+        <v>0.6850174216027874</v>
       </c>
       <c r="W3">
-        <v>0.1102123356926188</v>
+        <v>0.1234908589168679</v>
       </c>
       <c r="X3">
-        <v>0.1533664349255993</v>
+        <v>0.1717476116012148</v>
       </c>
       <c r="Y3">
-        <v>-0.04315409923298048</v>
+        <v>-0.04825675268434694</v>
       </c>
       <c r="Z3">
-        <v>0.2014472455648926</v>
+        <v>0.1831275720164609</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06909781788540025</v>
+        <v>0.0890883295237552</v>
       </c>
       <c r="AC3">
-        <v>-0.06909781788540025</v>
+        <v>-0.0890883295237552</v>
       </c>
       <c r="AD3">
-        <v>389.8</v>
+        <v>432</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>389.8</v>
+        <v>432</v>
       </c>
       <c r="AG3">
-        <v>189.4</v>
+        <v>333.7</v>
       </c>
       <c r="AH3">
-        <v>0.7206507672397856</v>
+        <v>0.7506516072980017</v>
       </c>
       <c r="AI3">
-        <v>0.6458989229494615</v>
+        <v>0.6171428571428571</v>
       </c>
       <c r="AJ3">
-        <v>0.5562408223201175</v>
+        <v>0.699287510477787</v>
       </c>
       <c r="AK3">
-        <v>0.4698585958819151</v>
+        <v>0.5545953132790427</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mercantile Bank Limited (DSE:MERCANBANK)</t>
+          <t>ONE Bank Limited (DSE:ONEBANKLTD)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0622</v>
+        <v>-0.05110000000000001</v>
       </c>
       <c r="E4">
-        <v>0.126</v>
+        <v>-0.333</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>47.5</v>
+        <v>3.97</v>
       </c>
       <c r="L4">
-        <v>0.301970756516211</v>
+        <v>0.06145510835913313</v>
       </c>
       <c r="M4">
-        <v>18.9</v>
+        <v>0.042</v>
       </c>
       <c r="N4">
-        <v>0.09126026074360212</v>
+        <v>0.0004316546762589928</v>
       </c>
       <c r="O4">
-        <v>0.3978947368421052</v>
+        <v>0.01057934508816121</v>
       </c>
       <c r="P4">
-        <v>18.9</v>
+        <v>0.042</v>
       </c>
       <c r="Q4">
-        <v>0.09126026074360212</v>
+        <v>0.0004316546762589928</v>
       </c>
       <c r="R4">
-        <v>0.3978947368421052</v>
+        <v>0.01057934508816121</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,176 +880,60 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>101.6</v>
+        <v>137.3</v>
       </c>
       <c r="V4">
-        <v>0.490584258812168</v>
+        <v>1.411099691675231</v>
       </c>
       <c r="W4">
-        <v>0.1812977099236641</v>
+        <v>0.01861228316924519</v>
       </c>
       <c r="X4">
-        <v>0.1544241428707464</v>
+        <v>0.184213902609081</v>
       </c>
       <c r="Y4">
-        <v>0.02687356705291774</v>
+        <v>-0.1656016194398358</v>
       </c>
       <c r="Z4">
-        <v>0.2724281260824385</v>
+        <v>0.1604171840079463</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06910969159285622</v>
+        <v>0.08929167955707415</v>
       </c>
       <c r="AC4">
-        <v>-0.06910969159285622</v>
+        <v>-0.08929167955707415</v>
       </c>
       <c r="AD4">
-        <v>540.7</v>
+        <v>333.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>540.7</v>
+        <v>333.9</v>
       </c>
       <c r="AG4">
-        <v>439.1</v>
+        <v>196.6</v>
       </c>
       <c r="AH4">
-        <v>0.723054292591602</v>
+        <v>0.7743506493506493</v>
       </c>
       <c r="AI4">
-        <v>0.6500360663621063</v>
+        <v>0.6455916473317864</v>
       </c>
       <c r="AJ4">
-        <v>0.6795109873104302</v>
+        <v>0.6689350119088124</v>
       </c>
       <c r="AK4">
-        <v>0.6013420980553273</v>
+        <v>0.5175046064753882</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ICB Islamic Bank Limited (DSE:ICBIBANK)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.456</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>-4.71</v>
-      </c>
-      <c r="L5">
-        <v>-28.71951219512195</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>7.54</v>
-      </c>
-      <c r="V5">
-        <v>0.1861728395061728</v>
-      </c>
-      <c r="W5">
-        <v>0.0345307917888563</v>
-      </c>
-      <c r="X5">
-        <v>0.1129491680298411</v>
-      </c>
-      <c r="Y5">
-        <v>-0.07841837624098476</v>
-      </c>
-      <c r="Z5">
-        <v>-0.001763440860215054</v>
-      </c>
-      <c r="AA5">
-        <v>-0</v>
-      </c>
-      <c r="AB5">
-        <v>0.07022732727328164</v>
-      </c>
-      <c r="AC5">
-        <v>-0.07022732727328164</v>
-      </c>
-      <c r="AD5">
-        <v>56.4</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>56.4</v>
-      </c>
-      <c r="AG5">
-        <v>48.86</v>
-      </c>
-      <c r="AH5">
-        <v>0.5820433436532507</v>
-      </c>
-      <c r="AI5">
-        <v>-0.6658795749704841</v>
-      </c>
-      <c r="AJ5">
-        <v>0.5467770814682185</v>
-      </c>
-      <c r="AK5">
-        <v>-0.529705117085863</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/bangladesh/bangladesh_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.01055</v>
+        <v>0.0124</v>
       </c>
       <c r="E2">
-        <v>-0.15405</v>
+        <v>-0.172</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>39.77</v>
+        <v>10.5</v>
       </c>
       <c r="L2">
-        <v>0.2007571933366986</v>
+        <v>0.1098326359832636</v>
       </c>
       <c r="M2">
-        <v>12.842</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N2">
-        <v>0.05333056478405315</v>
+        <v>0.07347242921013412</v>
       </c>
       <c r="O2">
-        <v>0.3229067136032185</v>
+        <v>0.939047619047619</v>
       </c>
       <c r="P2">
-        <v>12.842</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.05333056478405315</v>
+        <v>0.07347242921013412</v>
       </c>
       <c r="R2">
-        <v>0.3229067136032185</v>
+        <v>0.939047619047619</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>235.6</v>
+        <v>74.7</v>
       </c>
       <c r="V2">
-        <v>0.978405315614618</v>
+        <v>0.5566318926974665</v>
       </c>
       <c r="W2">
-        <v>0.07105157104305654</v>
+        <v>0.03932584269662921</v>
       </c>
       <c r="X2">
-        <v>0.1779807571051479</v>
+        <v>0.1227347391276276</v>
       </c>
       <c r="Y2">
-        <v>-0.1069291860620913</v>
+        <v>-0.0834088964309984</v>
       </c>
       <c r="Z2">
-        <v>0.1750463903861447</v>
+        <v>0.1591476610620942</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08919000454041467</v>
+        <v>0.0834417856755556</v>
       </c>
       <c r="AC2">
-        <v>-0.08919000454041467</v>
+        <v>-0.0834417856755556</v>
       </c>
       <c r="AD2">
-        <v>765.9</v>
+        <v>299.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>765.9</v>
+        <v>299.9</v>
       </c>
       <c r="AG2">
-        <v>530.3</v>
+        <v>225.2</v>
       </c>
       <c r="AH2">
-        <v>0.7608026224297209</v>
+        <v>0.6908546417876066</v>
       </c>
       <c r="AI2">
-        <v>0.6292310220177456</v>
+        <v>0.5517939282428702</v>
       </c>
       <c r="AJ2">
-        <v>0.6877188432109973</v>
+        <v>0.6265998887033946</v>
       </c>
       <c r="AK2">
-        <v>0.5402404237978811</v>
+        <v>0.4803754266211605</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mercantile Bank Limited (DSE:MERCANBANK)</t>
+          <t>Mercantile Bank PLC. (DSE:MERCANBANK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0722</v>
+        <v>0.0124</v>
       </c>
       <c r="E3">
-        <v>0.0249</v>
+        <v>-0.172</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>35.8</v>
+        <v>10.5</v>
       </c>
       <c r="L3">
-        <v>0.2681647940074906</v>
+        <v>0.1098326359832636</v>
       </c>
       <c r="M3">
-        <v>12.8</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N3">
-        <v>0.089198606271777</v>
+        <v>0.07347242921013412</v>
       </c>
       <c r="O3">
-        <v>0.3575418994413408</v>
+        <v>0.939047619047619</v>
       </c>
       <c r="P3">
-        <v>12.8</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.089198606271777</v>
+        <v>0.07347242921013412</v>
       </c>
       <c r="R3">
-        <v>0.3575418994413408</v>
+        <v>0.939047619047619</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,182 +758,60 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>98.3</v>
+        <v>74.7</v>
       </c>
       <c r="V3">
-        <v>0.6850174216027874</v>
+        <v>0.5566318926974665</v>
       </c>
       <c r="W3">
-        <v>0.1234908589168679</v>
+        <v>0.03932584269662921</v>
       </c>
       <c r="X3">
-        <v>0.1717476116012148</v>
+        <v>0.1227347391276276</v>
       </c>
       <c r="Y3">
-        <v>-0.04825675268434694</v>
+        <v>-0.0834088964309984</v>
       </c>
       <c r="Z3">
-        <v>0.1831275720164609</v>
+        <v>0.1591476610620942</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0890883295237552</v>
+        <v>0.0834417856755556</v>
       </c>
       <c r="AC3">
-        <v>-0.0890883295237552</v>
+        <v>-0.0834417856755556</v>
       </c>
       <c r="AD3">
-        <v>432</v>
+        <v>299.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>432</v>
+        <v>299.9</v>
       </c>
       <c r="AG3">
-        <v>333.7</v>
+        <v>225.2</v>
       </c>
       <c r="AH3">
-        <v>0.7506516072980017</v>
+        <v>0.6908546417876066</v>
       </c>
       <c r="AI3">
-        <v>0.6171428571428571</v>
+        <v>0.5517939282428702</v>
       </c>
       <c r="AJ3">
-        <v>0.699287510477787</v>
+        <v>0.6265998887033946</v>
       </c>
       <c r="AK3">
-        <v>0.5545953132790427</v>
+        <v>0.4803754266211605</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ONE Bank Limited (DSE:ONEBANKLTD)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.05110000000000001</v>
-      </c>
-      <c r="E4">
-        <v>-0.333</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>3.97</v>
-      </c>
-      <c r="L4">
-        <v>0.06145510835913313</v>
-      </c>
-      <c r="M4">
-        <v>0.042</v>
-      </c>
-      <c r="N4">
-        <v>0.0004316546762589928</v>
-      </c>
-      <c r="O4">
-        <v>0.01057934508816121</v>
-      </c>
-      <c r="P4">
-        <v>0.042</v>
-      </c>
-      <c r="Q4">
-        <v>0.0004316546762589928</v>
-      </c>
-      <c r="R4">
-        <v>0.01057934508816121</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>137.3</v>
-      </c>
-      <c r="V4">
-        <v>1.411099691675231</v>
-      </c>
-      <c r="W4">
-        <v>0.01861228316924519</v>
-      </c>
-      <c r="X4">
-        <v>0.184213902609081</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1656016194398358</v>
-      </c>
-      <c r="Z4">
-        <v>0.1604171840079463</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.08929167955707415</v>
-      </c>
-      <c r="AC4">
-        <v>-0.08929167955707415</v>
-      </c>
-      <c r="AD4">
-        <v>333.9</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>333.9</v>
-      </c>
-      <c r="AG4">
-        <v>196.6</v>
-      </c>
-      <c r="AH4">
-        <v>0.7743506493506493</v>
-      </c>
-      <c r="AI4">
-        <v>0.6455916473317864</v>
-      </c>
-      <c r="AJ4">
-        <v>0.6689350119088124</v>
-      </c>
-      <c r="AK4">
-        <v>0.5175046064753882</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>
